--- a/00_ReusableActions/Default.xlsx
+++ b/00_ReusableActions/Default.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="SpreadsheetGear 8.2.5.102"/>
   <workbookPr defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18075" windowHeight="9900" activeTab="8"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18075" windowHeight="9900" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,6 @@
     <sheet name="Close App" sheetId="6" r:id="rId6"/>
     <sheet name="Delete Order" sheetId="7" r:id="rId7"/>
     <sheet name="Select Flight" sheetId="8" r:id="rId8"/>
-    <sheet name="Order the flight" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="40001"/>
 </workbook>
@@ -582,18 +581,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.1"/>
-  <cols>
-    <col min="1" max="16384" width="9.078125" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.95" customFormat="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>